--- a/type_curve_library.xlsx
+++ b/type_curve_library.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://greyrockep.sharepoint.com/sites/GraniteRidge/Shared Documents/Deals/Appalachia/Type Curves/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{45EBAC6D-CD64-4046-80AD-BD347A776C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1CD1183-091E-460E-ACE4-27F29F2C4371}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="8_{45EBAC6D-CD64-4046-80AD-BD347A776C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1B4286C-45DF-4433-9FAF-E01C6A38D001}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{AFE823C4-4807-4209-AF98-78E6D288EBFC}"/>
+    <workbookView minimized="1" xWindow="42075" yWindow="3135" windowWidth="28800" windowHeight="15345" xr2:uid="{AFE823C4-4807-4209-AF98-78E6D288EBFC}"/>
   </bookViews>
   <sheets>
     <sheet name="tc_metadata" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="10">
   <si>
     <t>tc_name</t>
   </si>
@@ -64,6 +64,9 @@
   </si>
   <si>
     <t>gas</t>
+  </si>
+  <si>
+    <t>dry_gas_west</t>
   </si>
 </sst>
 </file>
@@ -464,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DFE2F79-E08B-477D-95DF-69E8F6762797}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="20.7109375" customWidth="1"/>
@@ -510,6 +513,14 @@
         <v>10000</v>
       </c>
     </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="3">
+        <v>15000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -517,7 +528,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0289ABD-A744-47E7-B614-CE7DF7FE1F7D}">
-  <dimension ref="A1:D1441"/>
+  <dimension ref="A1:D1801"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.7109375" customWidth="1"/>
@@ -20698,12 +20709,5094 @@
         <v>1341.44</v>
       </c>
     </row>
+    <row r="1442" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1442" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1442" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1442" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1442" s="3">
+        <v>310000</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1443" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1443" s="3">
+        <v>2</v>
+      </c>
+      <c r="C1443" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1443" s="3">
+        <v>634379.19999999995</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1444" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1444" s="3">
+        <v>3</v>
+      </c>
+      <c r="C1444" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1444" s="3">
+        <v>664849.69999999995</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1445" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1445" s="3">
+        <v>4</v>
+      </c>
+      <c r="C1445" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1445" s="3">
+        <v>652685.69999999995</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1446" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1446" s="3">
+        <v>5</v>
+      </c>
+      <c r="C1446" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1446" s="3">
+        <v>684316.4</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1447" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1447" s="3">
+        <v>6</v>
+      </c>
+      <c r="C1447" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1447" s="3">
+        <v>672080.1</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1448" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1448" s="3">
+        <v>7</v>
+      </c>
+      <c r="C1448" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1448" s="3">
+        <v>682047.5</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1449" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1449" s="3">
+        <v>8</v>
+      </c>
+      <c r="C1449" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1449" s="3">
+        <v>715572.6</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1450" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1450" s="3">
+        <v>9</v>
+      </c>
+      <c r="C1450" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1450" s="3">
+        <v>703254.6</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1451" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1451" s="3">
+        <v>10</v>
+      </c>
+      <c r="C1451" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1451" s="3">
+        <v>686526.1</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1452" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1452" s="3">
+        <v>11</v>
+      </c>
+      <c r="C1452" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1452" s="3">
+        <v>587894.19999999995</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1453" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1453" s="3">
+        <v>12</v>
+      </c>
+      <c r="C1453" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1453" s="3">
+        <v>527203.1</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1454" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1454" s="3">
+        <v>13</v>
+      </c>
+      <c r="C1454" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1454" s="3">
+        <v>492317.4</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1455" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1455" s="3">
+        <v>14</v>
+      </c>
+      <c r="C1455" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1455" s="3">
+        <v>433993.9</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1456" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1456" s="3">
+        <v>15</v>
+      </c>
+      <c r="C1456" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1456" s="3">
+        <v>411355.8</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1457" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1457" s="3">
+        <v>16</v>
+      </c>
+      <c r="C1457" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1457" s="3">
+        <v>367291.1</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1458" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1458" s="3">
+        <v>17</v>
+      </c>
+      <c r="C1458" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1458" s="3">
+        <v>352006.8</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1459" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1459" s="3">
+        <v>18</v>
+      </c>
+      <c r="C1459" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1459" s="3">
+        <v>317364</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1460" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1460" s="3">
+        <v>19</v>
+      </c>
+      <c r="C1460" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1460" s="3">
+        <v>297183.59999999998</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1461" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1461" s="3">
+        <v>20</v>
+      </c>
+      <c r="C1461" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1461" s="3">
+        <v>288278.59999999998</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1462" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1462" s="3">
+        <v>21</v>
+      </c>
+      <c r="C1462" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1462" s="3">
+        <v>262726.7</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1463" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1463" s="3">
+        <v>22</v>
+      </c>
+      <c r="C1463" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1463" s="3">
+        <v>256423.2</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1464" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1464" s="3">
+        <v>23</v>
+      </c>
+      <c r="C1464" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1464" s="3">
+        <v>234998</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1465" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1465" s="3">
+        <v>24</v>
+      </c>
+      <c r="C1465" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1465" s="3">
+        <v>223268.3</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1466" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1466" s="3">
+        <v>25</v>
+      </c>
+      <c r="C1466" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1466" s="3">
+        <v>219490.6</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1467" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1467" s="3">
+        <v>26</v>
+      </c>
+      <c r="C1467" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1467" s="3">
+        <v>202485.7</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1468" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1468" s="3">
+        <v>27</v>
+      </c>
+      <c r="C1468" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1468" s="3">
+        <v>199836.9</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1469" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1469" s="3">
+        <v>28</v>
+      </c>
+      <c r="C1469" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1469" s="3">
+        <v>185019.7</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1470" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1470" s="3">
+        <v>29</v>
+      </c>
+      <c r="C1470" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1470" s="3">
+        <v>183208.7</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1471" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1471" s="3">
+        <v>30</v>
+      </c>
+      <c r="C1471" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1471" s="3">
+        <v>170150.5</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1472" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1472" s="3">
+        <v>31</v>
+      </c>
+      <c r="C1472" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1472" s="3">
+        <v>163624.1</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1473" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1473" s="3">
+        <v>32</v>
+      </c>
+      <c r="C1473" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1473" s="3">
+        <v>162697.79999999999</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1474" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1474" s="3">
+        <v>33</v>
+      </c>
+      <c r="C1474" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1474" s="3">
+        <v>151690.5</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1475" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1475" s="3">
+        <v>34</v>
+      </c>
+      <c r="C1475" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1475" s="3">
+        <v>151188.5</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1476" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1476" s="3">
+        <v>35</v>
+      </c>
+      <c r="C1476" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1476" s="3">
+        <v>141273.1</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1477" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1477" s="3">
+        <v>36</v>
+      </c>
+      <c r="C1477" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1477" s="3">
+        <v>136622.70000000001</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1478" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1478" s="3">
+        <v>37</v>
+      </c>
+      <c r="C1478" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1478" s="3">
+        <v>136583.6</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1479" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1479" s="3">
+        <v>38</v>
+      </c>
+      <c r="C1479" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1479" s="3">
+        <v>127991.7</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1480" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1480" s="3">
+        <v>39</v>
+      </c>
+      <c r="C1480" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1480" s="3">
+        <v>128180.7</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1481" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1481" s="3">
+        <v>40</v>
+      </c>
+      <c r="C1481" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1481" s="3">
+        <v>120318.1</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1482" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1482" s="3">
+        <v>41</v>
+      </c>
+      <c r="C1482" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1482" s="3">
+        <v>120686.6</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1483" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1483" s="3">
+        <v>42</v>
+      </c>
+      <c r="C1483" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1483" s="3">
+        <v>113454.3</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1484" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1484" s="3">
+        <v>43</v>
+      </c>
+      <c r="C1484" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1484" s="3">
+        <v>110338.6</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1485" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1485" s="3">
+        <v>44</v>
+      </c>
+      <c r="C1485" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1485" s="3">
+        <v>110907.6</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1486" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1486" s="3">
+        <v>45</v>
+      </c>
+      <c r="C1486" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1486" s="3">
+        <v>104468.8</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1487" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1487" s="3">
+        <v>46</v>
+      </c>
+      <c r="C1487" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1487" s="3">
+        <v>105137.9</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1488" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1488" s="3">
+        <v>47</v>
+      </c>
+      <c r="C1488" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1488" s="3">
+        <v>99151.61</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1489" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1489" s="3">
+        <v>48</v>
+      </c>
+      <c r="C1489" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1489" s="3">
+        <v>96716.69</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1490" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1490" s="3">
+        <v>49</v>
+      </c>
+      <c r="C1490" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1490" s="3">
+        <v>97497.61</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1491" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1491" s="3">
+        <v>50</v>
+      </c>
+      <c r="C1491" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1491" s="3">
+        <v>92092.55</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1492" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1492" s="3">
+        <v>51</v>
+      </c>
+      <c r="C1492" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1492" s="3">
+        <v>92928.94</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1493" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1493" s="3">
+        <v>52</v>
+      </c>
+      <c r="C1493" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1493" s="3">
+        <v>87861.45</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1494" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1494" s="3">
+        <v>53</v>
+      </c>
+      <c r="C1494" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1494" s="3">
+        <v>88741.17</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1495" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1495" s="3">
+        <v>54</v>
+      </c>
+      <c r="C1495" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1495" s="3">
+        <v>83976.46</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1496" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1496" s="3">
+        <v>55</v>
+      </c>
+      <c r="C1496" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1496" s="3">
+        <v>82180.399999999994</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1497" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1497" s="3">
+        <v>56</v>
+      </c>
+      <c r="C1497" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1497" s="3">
+        <v>83107</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1498" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1498" s="3">
+        <v>57</v>
+      </c>
+      <c r="C1498" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1498" s="3">
+        <v>78739.539999999994</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1499" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1499" s="3">
+        <v>58</v>
+      </c>
+      <c r="C1499" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1499" s="3">
+        <v>79688.17</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1500" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1500" s="3">
+        <v>59</v>
+      </c>
+      <c r="C1500" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1500" s="3">
+        <v>75556.05</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1501" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1501" s="3">
+        <v>60</v>
+      </c>
+      <c r="C1501" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1501" s="3">
+        <v>74076.38</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1502" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1502" s="3">
+        <v>61</v>
+      </c>
+      <c r="C1502" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1502" s="3">
+        <v>75047.11</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1503" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1503" s="3">
+        <v>62</v>
+      </c>
+      <c r="C1503" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1503" s="3">
+        <v>71227.48</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1504" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1504" s="3">
+        <v>63</v>
+      </c>
+      <c r="C1504" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1504" s="3">
+        <v>72207.289999999994</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1505" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1505" s="3">
+        <v>64</v>
+      </c>
+      <c r="C1505" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1505" s="3">
+        <v>68574.86</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1506" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1506" s="3">
+        <v>65</v>
+      </c>
+      <c r="C1506" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1506" s="3">
+        <v>69560.070000000007</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1507" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1507" s="3">
+        <v>66</v>
+      </c>
+      <c r="C1507" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1507" s="3">
+        <v>66099.399999999994</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1508" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1508" s="3">
+        <v>67</v>
+      </c>
+      <c r="C1508" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1508" s="3">
+        <v>64941.75</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1509" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1509" s="3">
+        <v>68</v>
+      </c>
+      <c r="C1509" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1509" s="3">
+        <v>65929.55</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1510" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1510" s="3">
+        <v>69</v>
+      </c>
+      <c r="C1510" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1510" s="3">
+        <v>62700.05</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1511" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1511" s="3">
+        <v>70</v>
+      </c>
+      <c r="C1511" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1511" s="3">
+        <v>63686.65</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1512" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1512" s="3">
+        <v>71</v>
+      </c>
+      <c r="C1512" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1512" s="3">
+        <v>60597.42</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1513" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1513" s="3">
+        <v>72</v>
+      </c>
+      <c r="C1513" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1513" s="3">
+        <v>59610.57</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1514" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1514" s="3">
+        <v>73</v>
+      </c>
+      <c r="C1514" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1514" s="3">
+        <v>60591.99</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1515" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1515" s="3">
+        <v>74</v>
+      </c>
+      <c r="C1515" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1515" s="3">
+        <v>57693.08</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1516" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1516" s="3">
+        <v>75</v>
+      </c>
+      <c r="C1516" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1516" s="3">
+        <v>58669.21</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1517" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1517" s="3">
+        <v>76</v>
+      </c>
+      <c r="C1517" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1517" s="3">
+        <v>55886.67</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1518" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1518" s="3">
+        <v>77</v>
+      </c>
+      <c r="C1518" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1518" s="3">
+        <v>56856.35</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1519" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1519" s="3">
+        <v>78</v>
+      </c>
+      <c r="C1519" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1519" s="3">
+        <v>54182.17</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1520" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1520" s="3">
+        <v>79</v>
+      </c>
+      <c r="C1520" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1520" s="3">
+        <v>53378.76</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1521" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1521" s="3">
+        <v>80</v>
+      </c>
+      <c r="C1521" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1521" s="3">
+        <v>54337.14</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1522" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1522" s="3">
+        <v>81</v>
+      </c>
+      <c r="C1522" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1522" s="3">
+        <v>51811.38</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1523" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1523" s="3">
+        <v>82</v>
+      </c>
+      <c r="C1523" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1523" s="3">
+        <v>52761.27</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1524" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1524" s="3">
+        <v>83</v>
+      </c>
+      <c r="C1524" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1524" s="3">
+        <v>50327.06</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1525" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1525" s="3">
+        <v>84</v>
+      </c>
+      <c r="C1525" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1525" s="3">
+        <v>49625.61</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1526" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1526" s="3">
+        <v>85</v>
+      </c>
+      <c r="C1526" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1526" s="3">
+        <v>50561.86</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1527" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1527" s="3">
+        <v>86</v>
+      </c>
+      <c r="C1527" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1527" s="3">
+        <v>48253.75</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1528" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1528" s="3">
+        <v>87</v>
+      </c>
+      <c r="C1528" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1528" s="3">
+        <v>49180.35</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1529" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1529" s="3">
+        <v>88</v>
+      </c>
+      <c r="C1529" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1529" s="3">
+        <v>46950.44</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1530" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1530" s="3">
+        <v>89</v>
+      </c>
+      <c r="C1530" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1530" s="3">
+        <v>47867.09</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1531" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1531" s="3">
+        <v>90</v>
+      </c>
+      <c r="C1531" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1531" s="3">
+        <v>45710.79</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1532" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1532" s="3">
+        <v>91</v>
+      </c>
+      <c r="C1532" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1532" s="3">
+        <v>45123.11</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1533" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1533" s="3">
+        <v>92</v>
+      </c>
+      <c r="C1533" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1533" s="3">
+        <v>46024.51</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1534" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1534" s="3">
+        <v>93</v>
+      </c>
+      <c r="C1534" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1534" s="3">
+        <v>43970.31</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1535" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1535" s="3">
+        <v>94</v>
+      </c>
+      <c r="C1535" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1535" s="3">
+        <v>44861.3</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1536" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1536" s="3">
+        <v>95</v>
+      </c>
+      <c r="C1536" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1536" s="3">
+        <v>42870.83</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1537" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1537" s="3">
+        <v>96</v>
+      </c>
+      <c r="C1537" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1537" s="3">
+        <v>42348.58</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1538" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1538" s="3">
+        <v>97</v>
+      </c>
+      <c r="C1538" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1538" s="3">
+        <v>43223.92</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1539" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1539" s="3">
+        <v>98</v>
+      </c>
+      <c r="C1539" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1539" s="3">
+        <v>41322.199999999997</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1540" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1540" s="3">
+        <v>99</v>
+      </c>
+      <c r="C1540" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1540" s="3">
+        <v>42187</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1541" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1541" s="3">
+        <v>100</v>
+      </c>
+      <c r="C1541" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1541" s="3">
+        <v>40340.910000000003</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1542" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1542" s="3">
+        <v>101</v>
+      </c>
+      <c r="C1542" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1542" s="3">
+        <v>41195.18</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1543" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1543" s="3">
+        <v>102</v>
+      </c>
+      <c r="C1543" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1543" s="3">
+        <v>39401.879999999997</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1544" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1544" s="3">
+        <v>103</v>
+      </c>
+      <c r="C1544" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1544" s="3">
+        <v>38954.76</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1545" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1545" s="3">
+        <v>104</v>
+      </c>
+      <c r="C1545" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1545" s="3">
+        <v>39793.4</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1546" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1546" s="3">
+        <v>105</v>
+      </c>
+      <c r="C1546" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1546" s="3">
+        <v>38073.99</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1547" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1547" s="3">
+        <v>106</v>
+      </c>
+      <c r="C1547" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1547" s="3">
+        <v>38902.230000000003</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1548" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1548" s="3">
+        <v>107</v>
+      </c>
+      <c r="C1548" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1548" s="3">
+        <v>37229.370000000003</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1549" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1549" s="3">
+        <v>108</v>
+      </c>
+      <c r="C1549" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1549" s="3">
+        <v>36826.58</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1550" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1550" s="3">
+        <v>109</v>
+      </c>
+      <c r="C1550" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1550" s="3">
+        <v>37639.47</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1551" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1551" s="3">
+        <v>110</v>
+      </c>
+      <c r="C1551" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1551" s="3">
+        <v>36031.980000000003</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1552" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1552" s="3">
+        <v>111</v>
+      </c>
+      <c r="C1552" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1552" s="3">
+        <v>36834.720000000001</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1553" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1553" s="3">
+        <v>112</v>
+      </c>
+      <c r="C1553" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1553" s="3">
+        <v>35268.53</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1554" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1554" s="3">
+        <v>113</v>
+      </c>
+      <c r="C1554" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1554" s="3">
+        <v>36061.22</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1555" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1555" s="3">
+        <v>114</v>
+      </c>
+      <c r="C1555" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1555" s="3">
+        <v>34534.480000000003</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1556" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1556" s="3">
+        <v>115</v>
+      </c>
+      <c r="C1556" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1556" s="3">
+        <v>34183.75</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1557" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1557" s="3">
+        <v>116</v>
+      </c>
+      <c r="C1557" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1557" s="3">
+        <v>34961.69</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1558" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1558" s="3">
+        <v>117</v>
+      </c>
+      <c r="C1558" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1558" s="3">
+        <v>33490.57</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1559" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1559" s="3">
+        <v>118</v>
+      </c>
+      <c r="C1559" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1559" s="3">
+        <v>34258.79</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1560" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1560" s="3">
+        <v>119</v>
+      </c>
+      <c r="C1560" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1560" s="3">
+        <v>32822.949999999997</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1561" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1561" s="3">
+        <v>120</v>
+      </c>
+      <c r="C1561" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1561" s="3">
+        <v>32503.57</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1562" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1562" s="3">
+        <v>121</v>
+      </c>
+      <c r="C1562" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1562" s="3">
+        <v>33257.56</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1563" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1563" s="3">
+        <v>122</v>
+      </c>
+      <c r="C1563" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1563" s="3">
+        <v>31871.61</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1564" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1564" s="3">
+        <v>123</v>
+      </c>
+      <c r="C1564" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1564" s="3">
+        <v>32616.23</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1565" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1565" s="3">
+        <v>124</v>
+      </c>
+      <c r="C1565" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1565" s="3">
+        <v>31262</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1566" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1566" s="3">
+        <v>125</v>
+      </c>
+      <c r="C1566" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1566" s="3">
+        <v>31997.41</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1567" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1567" s="3">
+        <v>126</v>
+      </c>
+      <c r="C1567" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1567" s="3">
+        <v>30673.62</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1568" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1568" s="3">
+        <v>127</v>
+      </c>
+      <c r="C1568" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1568" s="3">
+        <v>30391.71</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1569" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1569" s="3">
+        <v>128</v>
+      </c>
+      <c r="C1569" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1569" s="3">
+        <v>31113.66</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1570" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1570" s="3">
+        <v>129</v>
+      </c>
+      <c r="C1570" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1570" s="3">
+        <v>29833.040000000001</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1571" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1571" s="3">
+        <v>130</v>
+      </c>
+      <c r="C1571" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1571" s="3">
+        <v>30546.15</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1572" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1572" s="3">
+        <v>131</v>
+      </c>
+      <c r="C1572" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1572" s="3">
+        <v>29293.08</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1573" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1573" s="3">
+        <v>132</v>
+      </c>
+      <c r="C1573" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1573" s="3">
+        <v>29034.11</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1574" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1574" s="3">
+        <v>133</v>
+      </c>
+      <c r="C1574" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1574" s="3">
+        <v>29734.32</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1575" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1575" s="3">
+        <v>134</v>
+      </c>
+      <c r="C1575" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1575" s="3">
+        <v>28520.400000000001</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1576" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1576" s="3">
+        <v>135</v>
+      </c>
+      <c r="C1576" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1576" s="3">
+        <v>29212.14</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1577" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1577" s="3">
+        <v>136</v>
+      </c>
+      <c r="C1577" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1577" s="3">
+        <v>28023.25</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1578" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1578" s="3">
+        <v>137</v>
+      </c>
+      <c r="C1578" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1578" s="3">
+        <v>28706.68</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1579" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1579" s="3">
+        <v>138</v>
+      </c>
+      <c r="C1579" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1579" s="3">
+        <v>27541.91</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1580" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1580" s="3">
+        <v>139</v>
+      </c>
+      <c r="C1580" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1580" s="3">
+        <v>27310.75</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1581" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1581" s="3">
+        <v>140</v>
+      </c>
+      <c r="C1581" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1581" s="3">
+        <v>27982.05</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1582" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1582" s="3">
+        <v>141</v>
+      </c>
+      <c r="C1582" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1582" s="3">
+        <v>26851.64</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1583" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1583" s="3">
+        <v>142</v>
+      </c>
+      <c r="C1583" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1583" s="3">
+        <v>27515</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1584" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1584" s="3">
+        <v>143</v>
+      </c>
+      <c r="C1584" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1584" s="3">
+        <v>26406.61</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1585" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1585" s="3">
+        <v>144</v>
+      </c>
+      <c r="C1585" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1585" s="3">
+        <v>26192.720000000001</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1586" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1586" s="3">
+        <v>145</v>
+      </c>
+      <c r="C1586" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1586" s="3">
+        <v>26844.48</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1587" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1587" s="3">
+        <v>146</v>
+      </c>
+      <c r="C1587" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1587" s="3">
+        <v>25767.54</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1588" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1588" s="3">
+        <v>147</v>
+      </c>
+      <c r="C1588" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1588" s="3">
+        <v>26411.71</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1589" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1589" s="3">
+        <v>148</v>
+      </c>
+      <c r="C1589" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1589" s="3">
+        <v>25354.959999999999</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1590" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1590" s="3">
+        <v>149</v>
+      </c>
+      <c r="C1590" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1590" s="3">
+        <v>25991.67</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1591" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1591" s="3">
+        <v>150</v>
+      </c>
+      <c r="C1591" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1591" s="3">
+        <v>24954.43</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1592" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1592" s="3">
+        <v>151</v>
+      </c>
+      <c r="C1592" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1592" s="3">
+        <v>24761.72</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1593" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1593" s="3">
+        <v>152</v>
+      </c>
+      <c r="C1593" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1593" s="3">
+        <v>25387.56</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1594" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1594" s="3">
+        <v>153</v>
+      </c>
+      <c r="C1594" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1594" s="3">
+        <v>24378.25</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1595" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1595" s="3">
+        <v>154</v>
+      </c>
+      <c r="C1595" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1595" s="3">
+        <v>24996.97</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1596" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1596" s="3">
+        <v>155</v>
+      </c>
+      <c r="C1596" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1596" s="3">
+        <v>24005.62</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1597" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1597" s="3">
+        <v>156</v>
+      </c>
+      <c r="C1597" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1597" s="3">
+        <v>23826.2</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1598" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1598" s="3">
+        <v>157</v>
+      </c>
+      <c r="C1598" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1598" s="3">
+        <v>24434.54</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1599" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1599" s="3">
+        <v>158</v>
+      </c>
+      <c r="C1599" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1599" s="3">
+        <v>23468.94</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1600" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1600" s="3">
+        <v>159</v>
+      </c>
+      <c r="C1600" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1600" s="3">
+        <v>24070.47</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1601" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1601" s="3">
+        <v>160</v>
+      </c>
+      <c r="C1601" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1601" s="3">
+        <v>23121.46</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1602" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1602" s="3">
+        <v>161</v>
+      </c>
+      <c r="C1602" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1602" s="3">
+        <v>23716.32</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1603" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1603" s="3">
+        <v>162</v>
+      </c>
+      <c r="C1603" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1603" s="3">
+        <v>22783.38</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1604" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1604" s="3">
+        <v>163</v>
+      </c>
+      <c r="C1604" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1604" s="3">
+        <v>22620.45</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1605" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1605" s="3">
+        <v>164</v>
+      </c>
+      <c r="C1605" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1605" s="3">
+        <v>23206.15</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1606" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1606" s="3">
+        <v>165</v>
+      </c>
+      <c r="C1606" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1606" s="3">
+        <v>22304.95</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1607" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1607" s="3">
+        <v>166</v>
+      </c>
+      <c r="C1607" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1607" s="3">
+        <v>22894.89</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1608" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1608" s="3">
+        <v>167</v>
+      </c>
+      <c r="C1608" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1608" s="3">
+        <v>22008.720000000001</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1609" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1609" s="3">
+        <v>168</v>
+      </c>
+      <c r="C1609" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1609" s="3">
+        <v>21864.48</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1610" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1610" s="3">
+        <v>169</v>
+      </c>
+      <c r="C1610" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1610" s="3">
+        <v>22442.77</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1611" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1611" s="3">
+        <v>170</v>
+      </c>
+      <c r="C1611" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1611" s="3">
+        <v>21574.1</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1612" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1612" s="3">
+        <v>171</v>
+      </c>
+      <c r="C1612" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1612" s="3">
+        <v>22144.71</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1613" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1613" s="3">
+        <v>172</v>
+      </c>
+      <c r="C1613" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1613" s="3">
+        <v>21287.58</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1614" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1614" s="3">
+        <v>173</v>
+      </c>
+      <c r="C1614" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1614" s="3">
+        <v>21850.61</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1615" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1615" s="3">
+        <v>174</v>
+      </c>
+      <c r="C1615" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1615" s="3">
+        <v>21004.86</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1616" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1616" s="3">
+        <v>175</v>
+      </c>
+      <c r="C1616" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1616" s="3">
+        <v>20867.2</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1617" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1617" s="3">
+        <v>176</v>
+      </c>
+      <c r="C1617" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1617" s="3">
+        <v>21419.11</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1618" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1618" s="3">
+        <v>177</v>
+      </c>
+      <c r="C1618" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1618" s="3">
+        <v>20590.07</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1619" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1619" s="3">
+        <v>178</v>
+      </c>
+      <c r="C1619" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1619" s="3">
+        <v>21134.65</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1620" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1620" s="3">
+        <v>179</v>
+      </c>
+      <c r="C1620" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1620" s="3">
+        <v>20316.61</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1621" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1621" s="3">
+        <v>180</v>
+      </c>
+      <c r="C1621" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1621" s="3">
+        <v>20183.46</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1622" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1622" s="3">
+        <v>181</v>
+      </c>
+      <c r="C1622" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1622" s="3">
+        <v>20717.29</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1623" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1623" s="3">
+        <v>182</v>
+      </c>
+      <c r="C1623" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1623" s="3">
+        <v>19915.41</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1624" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1624" s="3">
+        <v>183</v>
+      </c>
+      <c r="C1624" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1624" s="3">
+        <v>20442.14</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1625" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1625" s="3">
+        <v>184</v>
+      </c>
+      <c r="C1625" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1625" s="3">
+        <v>19650.91</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1626" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1626" s="3">
+        <v>185</v>
+      </c>
+      <c r="C1626" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1626" s="3">
+        <v>20170.650000000001</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1627" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1627" s="3">
+        <v>186</v>
+      </c>
+      <c r="C1627" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1627" s="3">
+        <v>19389.93</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1628" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1628" s="3">
+        <v>187</v>
+      </c>
+      <c r="C1628" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1628" s="3">
+        <v>19262.849999999999</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1629" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1629" s="3">
+        <v>188</v>
+      </c>
+      <c r="C1629" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1629" s="3">
+        <v>19772.330000000002</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1630" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1630" s="3">
+        <v>189</v>
+      </c>
+      <c r="C1630" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1630" s="3">
+        <v>19007.03</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1631" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1631" s="3">
+        <v>190</v>
+      </c>
+      <c r="C1631" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1631" s="3">
+        <v>19509.740000000002</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1632" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1632" s="3">
+        <v>191</v>
+      </c>
+      <c r="C1632" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1632" s="3">
+        <v>18754.599999999999</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1633" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1633" s="3">
+        <v>192</v>
+      </c>
+      <c r="C1633" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1633" s="3">
+        <v>18631.68</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1634" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1634" s="3">
+        <v>193</v>
+      </c>
+      <c r="C1634" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1634" s="3">
+        <v>19124.47</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1635" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1635" s="3">
+        <v>194</v>
+      </c>
+      <c r="C1635" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1635" s="3">
+        <v>18384.240000000002</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1636" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1636" s="3">
+        <v>195</v>
+      </c>
+      <c r="C1636" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1636" s="3">
+        <v>18870.48</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1637" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1637" s="3">
+        <v>196</v>
+      </c>
+      <c r="C1637" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1637" s="3">
+        <v>18140.080000000002</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1638" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1638" s="3">
+        <v>197</v>
+      </c>
+      <c r="C1638" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1638" s="3">
+        <v>18619.86</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1639" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1639" s="3">
+        <v>198</v>
+      </c>
+      <c r="C1639" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1639" s="3">
+        <v>17899.16</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1640" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1640" s="3">
+        <v>199</v>
+      </c>
+      <c r="C1640" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1640" s="3">
+        <v>17781.86</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1641" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1641" s="3">
+        <v>200</v>
+      </c>
+      <c r="C1641" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1641" s="3">
+        <v>18252.16</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1642" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1642" s="3">
+        <v>201</v>
+      </c>
+      <c r="C1642" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1642" s="3">
+        <v>17545.7</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1643" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1643" s="3">
+        <v>202</v>
+      </c>
+      <c r="C1643" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1643" s="3">
+        <v>18009.759999999998</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1644" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1644" s="3">
+        <v>203</v>
+      </c>
+      <c r="C1644" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1644" s="3">
+        <v>17312.669999999998</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1645" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1645" s="3">
+        <v>204</v>
+      </c>
+      <c r="C1645" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1645" s="3">
+        <v>17199.21</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1646" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1646" s="3">
+        <v>205</v>
+      </c>
+      <c r="C1646" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1646" s="3">
+        <v>17654.11</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1647" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1647" s="3">
+        <v>206</v>
+      </c>
+      <c r="C1647" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1647" s="3">
+        <v>16970.79</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1648" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1648" s="3">
+        <v>207</v>
+      </c>
+      <c r="C1648" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1648" s="3">
+        <v>17419.650000000001</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1649" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1649" s="3">
+        <v>208</v>
+      </c>
+      <c r="C1649" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1649" s="3">
+        <v>16745.400000000001</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1650" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1650" s="3">
+        <v>209</v>
+      </c>
+      <c r="C1650" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1650" s="3">
+        <v>17188.3</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1651" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1651" s="3">
+        <v>210</v>
+      </c>
+      <c r="C1651" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1651" s="3">
+        <v>16523.009999999998</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1652" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1652" s="3">
+        <v>211</v>
+      </c>
+      <c r="C1652" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1652" s="3">
+        <v>16414.72</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1653" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1653" s="3">
+        <v>212</v>
+      </c>
+      <c r="C1653" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1653" s="3">
+        <v>16848.87</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1654" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1654" s="3">
+        <v>213</v>
+      </c>
+      <c r="C1654" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1654" s="3">
+        <v>16196.72</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1655" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1655" s="3">
+        <v>214</v>
+      </c>
+      <c r="C1655" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1655" s="3">
+        <v>16625.099999999999</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1656" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1656" s="3">
+        <v>215</v>
+      </c>
+      <c r="C1656" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1656" s="3">
+        <v>15981.61</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1657" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1657" s="3">
+        <v>216</v>
+      </c>
+      <c r="C1657" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1657" s="3">
+        <v>15876.87</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1658" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1658" s="3">
+        <v>217</v>
+      </c>
+      <c r="C1658" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1658" s="3">
+        <v>16296.8</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1659" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1659" s="3">
+        <v>218</v>
+      </c>
+      <c r="C1659" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1659" s="3">
+        <v>15666.01</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1660" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1660" s="3">
+        <v>219</v>
+      </c>
+      <c r="C1660" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1660" s="3">
+        <v>16080.36</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1661" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1661" s="3">
+        <v>220</v>
+      </c>
+      <c r="C1661" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1661" s="3">
+        <v>15457.96</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1662" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1662" s="3">
+        <v>221</v>
+      </c>
+      <c r="C1662" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1662" s="3">
+        <v>15866.8</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1663" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1663" s="3">
+        <v>222</v>
+      </c>
+      <c r="C1663" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1663" s="3">
+        <v>15252.66</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1664" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1664" s="3">
+        <v>223</v>
+      </c>
+      <c r="C1664" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1664" s="3">
+        <v>15152.7</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1665" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1665" s="3">
+        <v>224</v>
+      </c>
+      <c r="C1665" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1665" s="3">
+        <v>15553.47</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1666" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1666" s="3">
+        <v>225</v>
+      </c>
+      <c r="C1666" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1666" s="3">
+        <v>14951.46</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1667" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1667" s="3">
+        <v>226</v>
+      </c>
+      <c r="C1667" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1667" s="3">
+        <v>15346.9</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1668" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1668" s="3">
+        <v>227</v>
+      </c>
+      <c r="C1668" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1668" s="3">
+        <v>14752.89</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1669" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1669" s="3">
+        <v>228</v>
+      </c>
+      <c r="C1669" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1669" s="3">
+        <v>14656.2</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1670" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1670" s="3">
+        <v>229</v>
+      </c>
+      <c r="C1670" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1670" s="3">
+        <v>15043.84</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1671" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1671" s="3">
+        <v>230</v>
+      </c>
+      <c r="C1671" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1671" s="3">
+        <v>14461.55</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1672" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1672" s="3">
+        <v>231</v>
+      </c>
+      <c r="C1672" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1672" s="3">
+        <v>14844.04</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1673" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1673" s="3">
+        <v>232</v>
+      </c>
+      <c r="C1673" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1673" s="3">
+        <v>14269.49</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1674" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1674" s="3">
+        <v>233</v>
+      </c>
+      <c r="C1674" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1674" s="3">
+        <v>14646.9</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1675" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1675" s="3">
+        <v>234</v>
+      </c>
+      <c r="C1675" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1675" s="3">
+        <v>14079.98</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1676" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1676" s="3">
+        <v>235</v>
+      </c>
+      <c r="C1676" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1676" s="3">
+        <v>13987.7</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1677" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1677" s="3">
+        <v>236</v>
+      </c>
+      <c r="C1677" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1677" s="3">
+        <v>14357.66</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1678" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1678" s="3">
+        <v>237</v>
+      </c>
+      <c r="C1678" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1678" s="3">
+        <v>13801.93</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1679" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1679" s="3">
+        <v>238</v>
+      </c>
+      <c r="C1679" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1679" s="3">
+        <v>14166.98</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1680" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1680" s="3">
+        <v>239</v>
+      </c>
+      <c r="C1680" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1680" s="3">
+        <v>13618.63</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1681" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1681" s="3">
+        <v>240</v>
+      </c>
+      <c r="C1681" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1681" s="3">
+        <v>13529.38</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1682" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1682" s="3">
+        <v>241</v>
+      </c>
+      <c r="C1682" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1682" s="3">
+        <v>13887.21</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1683" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1683" s="3">
+        <v>242</v>
+      </c>
+      <c r="C1683" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1683" s="3">
+        <v>13349.7</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1684" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1684" s="3">
+        <v>243</v>
+      </c>
+      <c r="C1684" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1684" s="3">
+        <v>13702.78</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1685" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1685" s="3">
+        <v>244</v>
+      </c>
+      <c r="C1685" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1685" s="3">
+        <v>13172.4</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1686" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1686" s="3">
+        <v>245</v>
+      </c>
+      <c r="C1686" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1686" s="3">
+        <v>13520.79</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1687" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1687" s="3">
+        <v>246</v>
+      </c>
+      <c r="C1687" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1687" s="3">
+        <v>12997.46</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1688" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1688" s="3">
+        <v>247</v>
+      </c>
+      <c r="C1688" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1688" s="3">
+        <v>12912.28</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1689" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1689" s="3">
+        <v>248</v>
+      </c>
+      <c r="C1689" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1689" s="3">
+        <v>13253.79</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1690" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1690" s="3">
+        <v>249</v>
+      </c>
+      <c r="C1690" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1690" s="3">
+        <v>12740.79</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1691" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1691" s="3">
+        <v>250</v>
+      </c>
+      <c r="C1691" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1691" s="3">
+        <v>13077.77</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1692" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1692" s="3">
+        <v>251</v>
+      </c>
+      <c r="C1692" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1692" s="3">
+        <v>12571.58</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1693" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1693" s="3">
+        <v>252</v>
+      </c>
+      <c r="C1693" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1693" s="3">
+        <v>12489.19</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1694" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1694" s="3">
+        <v>253</v>
+      </c>
+      <c r="C1694" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1694" s="3">
+        <v>12819.51</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1695" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1695" s="3">
+        <v>254</v>
+      </c>
+      <c r="C1695" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1695" s="3">
+        <v>12323.32</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1696" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1696" s="3">
+        <v>255</v>
+      </c>
+      <c r="C1696" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1696" s="3">
+        <v>12649.26</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1697" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1697" s="3">
+        <v>256</v>
+      </c>
+      <c r="C1697" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1697" s="3">
+        <v>12159.66</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1698" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1698" s="3">
+        <v>257</v>
+      </c>
+      <c r="C1698" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1698" s="3">
+        <v>12481.27</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1699" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1699" s="3">
+        <v>258</v>
+      </c>
+      <c r="C1699" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1699" s="3">
+        <v>11998.17</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1700" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1700" s="3">
+        <v>259</v>
+      </c>
+      <c r="C1700" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1700" s="3">
+        <v>11919.53</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1701" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1701" s="3">
+        <v>260</v>
+      </c>
+      <c r="C1701" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1701" s="3">
+        <v>12234.79</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1702" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1702" s="3">
+        <v>261</v>
+      </c>
+      <c r="C1702" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1702" s="3">
+        <v>11761.23</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1703" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1703" s="3">
+        <v>262</v>
+      </c>
+      <c r="C1703" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1703" s="3">
+        <v>12072.3</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1704" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1704" s="3">
+        <v>263</v>
+      </c>
+      <c r="C1704" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1704" s="3">
+        <v>11605.03</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1705" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1705" s="3">
+        <v>264</v>
+      </c>
+      <c r="C1705" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1705" s="3">
+        <v>11528.98</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1706" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1706" s="3">
+        <v>265</v>
+      </c>
+      <c r="C1706" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1706" s="3">
+        <v>11833.9</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1707" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1707" s="3">
+        <v>266</v>
+      </c>
+      <c r="C1707" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1707" s="3">
+        <v>11375.86</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1708" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1708" s="3">
+        <v>267</v>
+      </c>
+      <c r="C1708" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1708" s="3">
+        <v>11676.74</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1709" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1709" s="3">
+        <v>268</v>
+      </c>
+      <c r="C1709" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1709" s="3">
+        <v>11224.78</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1710" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1710" s="3">
+        <v>269</v>
+      </c>
+      <c r="C1710" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1710" s="3">
+        <v>11521.66</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1711" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1711" s="3">
+        <v>270</v>
+      </c>
+      <c r="C1711" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1711" s="3">
+        <v>11075.7</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1712" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1712" s="3">
+        <v>271</v>
+      </c>
+      <c r="C1712" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1712" s="3">
+        <v>11003.12</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1713" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1713" s="3">
+        <v>272</v>
+      </c>
+      <c r="C1713" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1713" s="3">
+        <v>11294.14</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1714" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1714" s="3">
+        <v>273</v>
+      </c>
+      <c r="C1714" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1714" s="3">
+        <v>10856.99</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1715" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1715" s="3">
+        <v>274</v>
+      </c>
+      <c r="C1715" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1715" s="3">
+        <v>11144.14</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1716" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1716" s="3">
+        <v>275</v>
+      </c>
+      <c r="C1716" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1716" s="3">
+        <v>10712.8</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1717" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1717" s="3">
+        <v>276</v>
+      </c>
+      <c r="C1717" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1717" s="3">
+        <v>10642.59</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1718" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1718" s="3">
+        <v>277</v>
+      </c>
+      <c r="C1718" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1718" s="3">
+        <v>10924.07</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1719" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1719" s="3">
+        <v>278</v>
+      </c>
+      <c r="C1719" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1719" s="3">
+        <v>10501.24</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1720" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1720" s="3">
+        <v>279</v>
+      </c>
+      <c r="C1720" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1720" s="3">
+        <v>10778.99</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1721" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1721" s="3">
+        <v>280</v>
+      </c>
+      <c r="C1721" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1721" s="3">
+        <v>10361.780000000001</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1722" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1722" s="3">
+        <v>281</v>
+      </c>
+      <c r="C1722" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1722" s="3">
+        <v>10635.83</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1723" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1723" s="3">
+        <v>282</v>
+      </c>
+      <c r="C1723" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1723" s="3">
+        <v>10224.16</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1724" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1724" s="3">
+        <v>283</v>
+      </c>
+      <c r="C1724" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1724" s="3">
+        <v>10157.16</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1725" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1725" s="3">
+        <v>284</v>
+      </c>
+      <c r="C1725" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1725" s="3">
+        <v>10425.799999999999</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1726" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1726" s="3">
+        <v>285</v>
+      </c>
+      <c r="C1726" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1726" s="3">
+        <v>10022.26</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1727" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1727" s="3">
+        <v>286</v>
+      </c>
+      <c r="C1727" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1727" s="3">
+        <v>10287.34</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1728" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1728" s="3">
+        <v>287</v>
+      </c>
+      <c r="C1728" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1728" s="3">
+        <v>9889.16</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1729" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1729" s="3">
+        <v>288</v>
+      </c>
+      <c r="C1729" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1729" s="3">
+        <v>9824.34</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1730" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1730" s="3">
+        <v>289</v>
+      </c>
+      <c r="C1730" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1730" s="3">
+        <v>10084.19</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1731" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1731" s="3">
+        <v>290</v>
+      </c>
+      <c r="C1731" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1731" s="3">
+        <v>9693.8700000000008</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1732" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1732" s="3">
+        <v>291</v>
+      </c>
+      <c r="C1732" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1732" s="3">
+        <v>9950.26</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1733" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1733" s="3">
+        <v>292</v>
+      </c>
+      <c r="C1733" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1733" s="3">
+        <v>9565.1299999999992</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1734" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1734" s="3">
+        <v>293</v>
+      </c>
+      <c r="C1734" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1734" s="3">
+        <v>9818.11</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1735" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1735" s="3">
+        <v>294</v>
+      </c>
+      <c r="C1735" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1735" s="3">
+        <v>9438.09</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1736" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1736" s="3">
+        <v>295</v>
+      </c>
+      <c r="C1736" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1736" s="3">
+        <v>9376.24</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1737" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1737" s="3">
+        <v>296</v>
+      </c>
+      <c r="C1737" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1737" s="3">
+        <v>9624.23</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1738" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1738" s="3">
+        <v>297</v>
+      </c>
+      <c r="C1738" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1738" s="3">
+        <v>9251.7099999999991</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1739" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1739" s="3">
+        <v>298</v>
+      </c>
+      <c r="C1739" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1739" s="3">
+        <v>9496.41</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1740" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1740" s="3">
+        <v>299</v>
+      </c>
+      <c r="C1740" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1740" s="3">
+        <v>9128.84</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1741" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1741" s="3">
+        <v>300</v>
+      </c>
+      <c r="C1741" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1741" s="3">
+        <v>9069.01</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1742" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1742" s="3">
+        <v>301</v>
+      </c>
+      <c r="C1742" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1742" s="3">
+        <v>9308.8799999999992</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1743" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1743" s="3">
+        <v>302</v>
+      </c>
+      <c r="C1743" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1743" s="3">
+        <v>8948.57</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1744" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1744" s="3">
+        <v>303</v>
+      </c>
+      <c r="C1744" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1744" s="3">
+        <v>9185.25</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1745" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1745" s="3">
+        <v>304</v>
+      </c>
+      <c r="C1745" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1745" s="3">
+        <v>8829.7199999999993</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1746" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1746" s="3">
+        <v>305</v>
+      </c>
+      <c r="C1746" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1746" s="3">
+        <v>9063.26</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1747" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1747" s="3">
+        <v>306</v>
+      </c>
+      <c r="C1747" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1747" s="3">
+        <v>8712.4599999999991</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1748" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1748" s="3">
+        <v>307</v>
+      </c>
+      <c r="C1748" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1748" s="3">
+        <v>8655.36</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1749" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1749" s="3">
+        <v>308</v>
+      </c>
+      <c r="C1749" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1749" s="3">
+        <v>8884.2800000000007</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1750" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1750" s="3">
+        <v>309</v>
+      </c>
+      <c r="C1750" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1750" s="3">
+        <v>8540.41</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1751" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1751" s="3">
+        <v>310</v>
+      </c>
+      <c r="C1751" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1751" s="3">
+        <v>8766.2900000000009</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1752" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1752" s="3">
+        <v>311</v>
+      </c>
+      <c r="C1752" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1752" s="3">
+        <v>8426.98</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1753" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1753" s="3">
+        <v>312</v>
+      </c>
+      <c r="C1753" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1753" s="3">
+        <v>8371.75</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1754" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1754" s="3">
+        <v>313</v>
+      </c>
+      <c r="C1754" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1754" s="3">
+        <v>8593.18</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1755" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1755" s="3">
+        <v>314</v>
+      </c>
+      <c r="C1755" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1755" s="3">
+        <v>8260.57</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1756" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1756" s="3">
+        <v>315</v>
+      </c>
+      <c r="C1756" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1756" s="3">
+        <v>8479.0499999999993</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1757" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1757" s="3">
+        <v>316</v>
+      </c>
+      <c r="C1757" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1757" s="3">
+        <v>8150.86</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1758" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1758" s="3">
+        <v>317</v>
+      </c>
+      <c r="C1758" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1758" s="3">
+        <v>8366.44</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1759" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1759" s="3">
+        <v>318</v>
+      </c>
+      <c r="C1759" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1759" s="3">
+        <v>8042.61</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1760" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1760" s="3">
+        <v>319</v>
+      </c>
+      <c r="C1760" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1760" s="3">
+        <v>7989.9</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1761" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1761" s="3">
+        <v>320</v>
+      </c>
+      <c r="C1761" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1761" s="3">
+        <v>8201.23</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1762" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1762" s="3">
+        <v>321</v>
+      </c>
+      <c r="C1762" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1762" s="3">
+        <v>7883.79</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1763" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1763" s="3">
+        <v>322</v>
+      </c>
+      <c r="C1763" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1763" s="3">
+        <v>8092.31</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1764" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1764" s="3">
+        <v>323</v>
+      </c>
+      <c r="C1764" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1764" s="3">
+        <v>7779.09</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1765" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1765" s="3">
+        <v>324</v>
+      </c>
+      <c r="C1765" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1765" s="3">
+        <v>7728.1</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1766" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1766" s="3">
+        <v>325</v>
+      </c>
+      <c r="C1766" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1766" s="3">
+        <v>7932.5</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1767" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1767" s="3">
+        <v>326</v>
+      </c>
+      <c r="C1767" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1767" s="3">
+        <v>7625.47</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1768" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1768" s="3">
+        <v>327</v>
+      </c>
+      <c r="C1768" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1768" s="3">
+        <v>7827.15</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1769" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1769" s="3">
+        <v>328</v>
+      </c>
+      <c r="C1769" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1769" s="3">
+        <v>7524.19</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1770" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1770" s="3">
+        <v>329</v>
+      </c>
+      <c r="C1770" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1770" s="3">
+        <v>7723.2</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1771" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1771" s="3">
+        <v>330</v>
+      </c>
+      <c r="C1771" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1771" s="3">
+        <v>7424.27</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1772" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1772" s="3">
+        <v>331</v>
+      </c>
+      <c r="C1772" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1772" s="3">
+        <v>7375.61</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1773" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1773" s="3">
+        <v>332</v>
+      </c>
+      <c r="C1773" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1773" s="3">
+        <v>7570.69</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1774" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1774" s="3">
+        <v>333</v>
+      </c>
+      <c r="C1774" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1774" s="3">
+        <v>7277.65</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1775" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1775" s="3">
+        <v>334</v>
+      </c>
+      <c r="C1775" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1775" s="3">
+        <v>7470.14</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1776" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1776" s="3">
+        <v>335</v>
+      </c>
+      <c r="C1776" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1776" s="3">
+        <v>7181</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1777" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1777" s="3">
+        <v>336</v>
+      </c>
+      <c r="C1777" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1777" s="3">
+        <v>7133.94</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1778" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1778" s="3">
+        <v>337</v>
+      </c>
+      <c r="C1778" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1778" s="3">
+        <v>7322.62</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1779" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1779" s="3">
+        <v>338</v>
+      </c>
+      <c r="C1779" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1779" s="3">
+        <v>7039.19</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1780" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1780" s="3">
+        <v>339</v>
+      </c>
+      <c r="C1780" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1780" s="3">
+        <v>7225.37</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1781" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1781" s="3">
+        <v>340</v>
+      </c>
+      <c r="C1781" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1781" s="3">
+        <v>6945.71</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1782" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1782" s="3">
+        <v>341</v>
+      </c>
+      <c r="C1782" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1782" s="3">
+        <v>7129.41</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1783" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1783" s="3">
+        <v>342</v>
+      </c>
+      <c r="C1783" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1783" s="3">
+        <v>6853.46</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1784" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1784" s="3">
+        <v>343</v>
+      </c>
+      <c r="C1784" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1784" s="3">
+        <v>6808.55</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1785" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1785" s="3">
+        <v>344</v>
+      </c>
+      <c r="C1785" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1785" s="3">
+        <v>6988.62</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1786" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1786" s="3">
+        <v>345</v>
+      </c>
+      <c r="C1786" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1786" s="3">
+        <v>6718.12</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1787" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1787" s="3">
+        <v>346</v>
+      </c>
+      <c r="C1787" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1787" s="3">
+        <v>6895.81</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1788" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1788" s="3">
+        <v>347</v>
+      </c>
+      <c r="C1788" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1788" s="3">
+        <v>6628.9</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1789" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1789" s="3">
+        <v>348</v>
+      </c>
+      <c r="C1789" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1789" s="3">
+        <v>6585.46</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1790" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1790" s="3">
+        <v>349</v>
+      </c>
+      <c r="C1790" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1790" s="3">
+        <v>6759.63</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1791" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1791" s="3">
+        <v>350</v>
+      </c>
+      <c r="C1791" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1791" s="3">
+        <v>6497.99</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1792" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1792" s="3">
+        <v>351</v>
+      </c>
+      <c r="C1792" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1792" s="3">
+        <v>6669.86</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1793" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1793" s="3">
+        <v>352</v>
+      </c>
+      <c r="C1793" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1793" s="3">
+        <v>6411.7</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1794" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1794" s="3">
+        <v>353</v>
+      </c>
+      <c r="C1794" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1794" s="3">
+        <v>6581.28</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1795" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1795" s="3">
+        <v>354</v>
+      </c>
+      <c r="C1795" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1795" s="3">
+        <v>6326.54</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1796" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1796" s="3">
+        <v>355</v>
+      </c>
+      <c r="C1796" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1796" s="3">
+        <v>6285.08</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1797" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1797" s="3">
+        <v>356</v>
+      </c>
+      <c r="C1797" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1797" s="3">
+        <v>6451.31</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1798" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1798" s="3">
+        <v>357</v>
+      </c>
+      <c r="C1798" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1798" s="3">
+        <v>6201.61</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1799" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1799" s="3">
+        <v>358</v>
+      </c>
+      <c r="C1799" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1799" s="3">
+        <v>6365.63</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1800" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1800" s="3">
+        <v>359</v>
+      </c>
+      <c r="C1800" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1800" s="3">
+        <v>6119.25</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1801" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1801" s="3">
+        <v>360</v>
+      </c>
+      <c r="C1801" s="3">
+        <v>0</v>
+      </c>
+      <c r="D1801" s="3">
+        <v>6079.14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalAssignedTo>
+    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalSentBy>
+    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
+    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </_ApprovalRespondedBy>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001D031D5A8E6EE6428A53B0E53476CCDA" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="001c387f81cf0a37189a660d3a02c4eb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9" xmlns:ns3="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7b945eefb7f5e1f0b5628c6881a66f9" ns2:_="" ns3:_="">
     <xsd:import namespace="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
@@ -20998,56 +26091,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ApprovalAssignedTo xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalAssignedTo>
-    <_ApprovalSentBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalSentBy>
-    <_ApprovalStatus xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">0</_ApprovalStatus>
-    <_ApprovalRespondedBy xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </_ApprovalRespondedBy>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="0aec0d96-7e21-4ccf-bb64-a3f8c6176559" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D68565D5-5088-4E54-98C1-C8B7DBD2C2AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62BFA16F-34C2-4417-AC65-9517E559B274}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
+    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AFCC776-2325-4B23-BB83-CFC7E05ABEC7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AFCC776-2325-4B23-BB83-CFC7E05ABEC7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62BFA16F-34C2-4417-AC65-9517E559B274}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D68565D5-5088-4E54-98C1-C8B7DBD2C2AF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1d031c3d-4611-4b37-8c0b-0a0e0dca67d9"/>
+    <ds:schemaRef ds:uri="0aec0d96-7e21-4ccf-bb64-a3f8c6176559"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>